--- a/Supplementary Data 1 - Metadata and Codebook.xlsx
+++ b/Supplementary Data 1 - Metadata and Codebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kschne34\Dropbox\GitHub\FSCI2025_Performance_Replication\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACAACCE-F5E4-4BF9-AC4A-E53333F6258B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A39DCD5-99DD-442F-9DE0-A91275112CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="758" xr2:uid="{627FC470-C124-47B7-9254-ED9E29476D78}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="758" activeTab="2" xr2:uid="{627FC470-C124-47B7-9254-ED9E29476D78}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="30" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4725" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4727" uniqueCount="1179">
   <si>
     <t>Food Systems Countdown Initiative</t>
   </si>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="B4" s="6">
         <f ca="1">TODAY()</f>
-        <v>46121</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -9614,7 +9614,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>373</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
         <v>376</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
         <v>379</v>
       </c>
@@ -9677,7 +9677,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>407</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>431</v>
       </c>
@@ -9719,7 +9719,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>435</v>
       </c>
@@ -9740,7 +9740,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>439</v>
       </c>
@@ -9760,8 +9760,14 @@
       <c r="G87" s="8" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H87" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>539</v>
       </c>
@@ -9781,8 +9787,14 @@
       <c r="G88" s="8" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H88" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="I88">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="7"/>
@@ -9790,7 +9802,7 @@
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="7"/>
@@ -9798,7 +9810,7 @@
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="7"/>
@@ -9806,7 +9818,7 @@
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="7"/>
@@ -9814,7 +9826,7 @@
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="7"/>
@@ -9822,7 +9834,7 @@
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="7"/>
@@ -9830,12 +9842,12 @@
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="7"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="7"/>
@@ -48711,21 +48723,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010018141AFBEDAA4E4F8F497BA0BA465628" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="51632a301ac108a956373b15242a2c1c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3740b2bf-318f-4c2d-92fe-b8cc5ab95724" xmlns:ns4="0d38da4c-d0a5-4e53-81d3-71f1e08ba0ee" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8aed9f36c2f7cc18b5698afd23e33de4" ns3:_="" ns4:_="">
     <xsd:import namespace="3740b2bf-318f-4c2d-92fe-b8cc5ab95724"/>
@@ -48954,24 +48951,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2FF79C2-D6CA-4146-8A33-8B2F68A6926A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8B78A5C-B87B-48A6-A425-F525FA87B0A7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{629B1C7C-1368-414C-B746-5D693F4D5577}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -48988,4 +48983,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8B78A5C-B87B-48A6-A425-F525FA87B0A7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2FF79C2-D6CA-4146-8A33-8B2F68A6926A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Supplementary Data 1 - Metadata and Codebook.xlsx
+++ b/Supplementary Data 1 - Metadata and Codebook.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kschne34\Dropbox\GitHub\FSCI2025_Performance_Replication\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kschne34\Dropbox (Personal)\GitHub\FSCI2025_Performance_Replication\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A39DCD5-99DD-442F-9DE0-A91275112CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DEDDAC-9883-4602-86B6-571982DB0E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="758" activeTab="2" xr2:uid="{627FC470-C124-47B7-9254-ED9E29476D78}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="758" activeTab="1" xr2:uid="{627FC470-C124-47B7-9254-ED9E29476D78}"/>
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="30" r:id="rId1"/>
@@ -3634,12 +3634,6 @@
     <t>fs_emissions_change</t>
   </si>
   <si>
-    <t>Percent change relative to 2000-2010 country average baseline</t>
-  </si>
-  <si>
-    <t>Baseline calculated at country level as average total agrifood system greenhouse gas emissions over the 2000-2010 period. Emissions change calculated as (annual total - baseline value) / baseline value</t>
-  </si>
-  <si>
     <t>Agri-food systems greenhouse gas emissions change</t>
   </si>
   <si>
@@ -3678,6 +3672,12 @@
   </si>
   <si>
     <t>Creators:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline calculated at country level as average total agrifood system greenhouse gas emissions over the 2000-2010 period. Emissions change calculated as (((annual total - baseline value) / baseline value) * 100)+100) to scale 0 =100 for interpretability </t>
+  </si>
+  <si>
+    <t>% change relative to 2000-2010 country average baseline, scaled to 0 = 100 for interpretability</t>
   </si>
 </sst>
 </file>
@@ -4292,53 +4292,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE1E5344-AFD3-48AB-8D86-002B38EED152}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="140.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="140.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="6">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>4</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
@@ -4378,12 +4378,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -4400,23 +4400,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51B5272-3AF0-4A29-83DE-88601F611647}">
   <dimension ref="A1:L88"/>
-  <sheetFormatPr defaultColWidth="50.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="50.81640625" defaultRowHeight="14" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.85546875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="42.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="79.81640625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" style="9" customWidth="1"/>
     <col min="5" max="5" width="24" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" style="9" customWidth="1"/>
-    <col min="7" max="7" width="34.85546875" style="9" customWidth="1"/>
-    <col min="8" max="8" width="40.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="38.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="69.5703125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="32.85546875" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="50.85546875" style="1"/>
+    <col min="6" max="6" width="29.7265625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="34.81640625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="40.26953125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="38.54296875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="69.54296875" style="8" customWidth="1"/>
+    <col min="11" max="11" width="32.81640625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="50.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>16</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>29</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>58</v>
@@ -4630,7 +4630,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -4665,7 +4665,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -4802,7 +4802,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>112</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>112</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>112</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>112</v>
       </c>
@@ -5144,7 +5144,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="26" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>112</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" s="26" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>112</v>
       </c>
@@ -5198,19 +5198,19 @@
       <c r="G23" s="19"/>
       <c r="H23" s="25"/>
       <c r="I23" s="10" t="s">
-        <v>1165</v>
+        <v>1177</v>
       </c>
       <c r="J23" s="21" t="s">
         <v>44</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>1164</v>
+        <v>1178</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="26" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>112</v>
       </c>
@@ -5248,7 +5248,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" s="26" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>112</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>138</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="J25" s="21" t="s">
         <v>44</v>
@@ -5286,7 +5286,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" s="26" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>112</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>138</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="J26" s="21" t="s">
         <v>44</v>
@@ -5324,7 +5324,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" s="26" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>112</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" s="26" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>112</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>138</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="J28" s="21" t="s">
         <v>44</v>
@@ -5400,7 +5400,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>112</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>112</v>
       </c>
@@ -5469,7 +5469,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>112</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>112</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>112</v>
       </c>
@@ -5565,7 +5565,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>112</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>192</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>192</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>192</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>192</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>192</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>192</v>
       </c>
@@ -5764,7 +5764,7 @@
         <v>222</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="1" t="s">
@@ -5788,7 +5788,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>192</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>231</v>
       </c>
@@ -5849,7 +5849,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>231</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>231</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>232</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>245</v>
@@ -5917,7 +5917,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>231</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>231</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>231</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>231</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>231</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>231</v>
       </c>
@@ -6117,7 +6117,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>231</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
         <v>288</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>288</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>288</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" s="26" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
         <v>288</v>
       </c>
@@ -6285,7 +6285,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>288</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>288</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>288</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" s="26" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="12" t="s">
         <v>288</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>288</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>288</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>350</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>350</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>350</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>350</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>350</v>
       </c>
@@ -6664,7 +6664,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>350</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>350</v>
       </c>
@@ -6734,7 +6734,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>350</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>350</v>
       </c>
@@ -6802,7 +6802,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>350</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>350</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>350</v>
       </c>
@@ -6900,7 +6900,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>350</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>350</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
         <v>350</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>350</v>
       </c>
@@ -7019,7 +7019,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>350</v>
       </c>
@@ -7047,7 +7047,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>350</v>
       </c>
@@ -7077,7 +7077,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>350</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>350</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>350</v>
       </c>
@@ -7171,7 +7171,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>350</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>350</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>350</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>350</v>
       </c>
@@ -7278,7 +7278,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>350</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>350</v>
       </c>
@@ -7441,23 +7441,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I202"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" style="8" customWidth="1"/>
-    <col min="2" max="2" width="77.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" style="16" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="33.42578125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="8" customWidth="1"/>
-    <col min="7" max="7" width="30.7109375" style="8" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="15.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.54296875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="31.7265625" style="16" customWidth="1"/>
+    <col min="4" max="4" width="14.54296875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="33.453125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="30.7265625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15.7265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.1796875" style="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.7109375" style="8"/>
+    <col min="14" max="16384" width="8.7265625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="13" customFormat="1" ht="14" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>442</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>451</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>453</v>
       </c>
@@ -7526,7 +7526,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>454</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>421</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>426</v>
       </c>
@@ -7586,7 +7586,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>391</v>
       </c>
@@ -7606,7 +7606,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>459</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>382</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>416</v>
       </c>
@@ -7666,7 +7666,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>403</v>
       </c>
@@ -7686,7 +7686,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>410</v>
       </c>
@@ -7706,7 +7706,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>31</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>40</v>
       </c>
@@ -7764,7 +7764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>48</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>51</v>
       </c>
@@ -7822,12 +7822,12 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>58</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>469</v>
@@ -7851,7 +7851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>66</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>72</v>
       </c>
@@ -7909,7 +7909,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="14" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>76</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>80</v>
       </c>
@@ -7967,7 +7967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>87</v>
       </c>
@@ -7996,7 +7996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>94</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>97</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>100</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="14" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>102</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>105</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>107</v>
       </c>
@@ -8170,7 +8170,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>116</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>121</v>
       </c>
@@ -8228,7 +8228,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>124</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>127</v>
       </c>
@@ -8286,7 +8286,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
         <v>130</v>
       </c>
@@ -8315,15 +8315,15 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>1163</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="D34" s="1">
         <v>22</v>
@@ -8344,7 +8344,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
         <v>136</v>
       </c>
@@ -8373,7 +8373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
         <v>142</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
         <v>146</v>
       </c>
@@ -8431,7 +8431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A38" s="15" t="s">
         <v>148</v>
       </c>
@@ -8460,7 +8460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
         <v>150</v>
       </c>
@@ -8489,7 +8489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="14" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>155</v>
       </c>
@@ -8518,7 +8518,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>163</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>170</v>
       </c>
@@ -8576,7 +8576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>177</v>
       </c>
@@ -8605,7 +8605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>184</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="14" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>190</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="14" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>195</v>
       </c>
@@ -8692,7 +8692,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>201</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>208</v>
       </c>
@@ -8750,7 +8750,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>213</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>220</v>
       </c>
@@ -8808,12 +8808,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>223</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>499</v>
@@ -8837,7 +8837,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>228</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>234</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>239</v>
       </c>
@@ -8924,12 +8924,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>245</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>504</v>
@@ -8953,7 +8953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>251</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>258</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>264</v>
       </c>
@@ -9040,7 +9040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="14" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>268</v>
       </c>
@@ -9069,7 +9069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>275</v>
       </c>
@@ -9098,7 +9098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>280</v>
       </c>
@@ -9127,7 +9127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>283</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
         <v>291</v>
       </c>
@@ -9185,7 +9185,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>300</v>
       </c>
@@ -9214,7 +9214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>305</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
         <v>309</v>
       </c>
@@ -9272,7 +9272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>315</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>320</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>325</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>332</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>340</v>
       </c>
@@ -9417,7 +9417,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="14" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
         <v>344</v>
       </c>
@@ -9446,7 +9446,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>412</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>523</v>
       </c>
@@ -9488,7 +9488,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>352</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>356</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>359</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>363</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>366</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="8" t="s">
         <v>369</v>
       </c>
@@ -9614,7 +9614,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="8" t="s">
         <v>373</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="8" t="s">
         <v>376</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="8" t="s">
         <v>379</v>
       </c>
@@ -9677,7 +9677,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>407</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>431</v>
       </c>
@@ -9719,7 +9719,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>435</v>
       </c>
@@ -9740,7 +9740,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>439</v>
       </c>
@@ -9767,7 +9767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>539</v>
       </c>
@@ -9794,7 +9794,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="7"/>
@@ -9802,7 +9802,7 @@
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="7"/>
@@ -9810,7 +9810,7 @@
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="7"/>
@@ -9818,7 +9818,7 @@
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="7"/>
@@ -9826,7 +9826,7 @@
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="7"/>
@@ -9834,7 +9834,7 @@
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="7"/>
@@ -9842,12 +9842,12 @@
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="7"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="7"/>
@@ -9855,7 +9855,7 @@
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="7"/>
@@ -9863,7 +9863,7 @@
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="7"/>
@@ -9871,7 +9871,7 @@
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="7"/>
@@ -9879,7 +9879,7 @@
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="7"/>
@@ -9887,7 +9887,7 @@
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="7"/>
@@ -9895,7 +9895,7 @@
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="7"/>
@@ -9903,7 +9903,7 @@
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="7"/>
@@ -9911,7 +9911,7 @@
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="7"/>
@@ -9919,7 +9919,7 @@
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="7"/>
@@ -9927,7 +9927,7 @@
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="7"/>
@@ -9935,7 +9935,7 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="7"/>
@@ -9943,7 +9943,7 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="7"/>
@@ -9951,7 +9951,7 @@
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="7"/>
@@ -9959,7 +9959,7 @@
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="7"/>
@@ -9967,7 +9967,7 @@
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="7"/>
@@ -9975,7 +9975,7 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="7"/>
@@ -9983,7 +9983,7 @@
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="7"/>
@@ -9991,7 +9991,7 @@
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="7"/>
@@ -9999,7 +9999,7 @@
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="7"/>
@@ -10007,7 +10007,7 @@
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="7"/>
@@ -10015,7 +10015,7 @@
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="7"/>
@@ -10023,7 +10023,7 @@
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="7"/>
@@ -10031,7 +10031,7 @@
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="7"/>
@@ -10039,7 +10039,7 @@
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="7"/>
@@ -10047,7 +10047,7 @@
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="7"/>
@@ -10055,7 +10055,7 @@
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="7"/>
@@ -10063,21 +10063,21 @@
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="14"/>
       <c r="B123" s="1"/>
       <c r="C123" s="7"/>
       <c r="D123" s="1"/>
       <c r="F123" s="1"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="14"/>
       <c r="B124" s="1"/>
       <c r="C124" s="7"/>
       <c r="D124" s="1"/>
       <c r="F124" s="1"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="14"/>
       <c r="B125" s="1"/>
       <c r="C125" s="7"/>
@@ -10085,56 +10085,56 @@
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="14"/>
       <c r="B126" s="1"/>
       <c r="C126" s="7"/>
       <c r="D126" s="1"/>
       <c r="F126" s="1"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="14"/>
       <c r="B127" s="1"/>
       <c r="C127" s="7"/>
       <c r="D127" s="1"/>
       <c r="F127" s="1"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="14"/>
       <c r="B128" s="1"/>
       <c r="C128" s="7"/>
       <c r="D128" s="1"/>
       <c r="F128" s="1"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="14"/>
       <c r="B129" s="1"/>
       <c r="C129" s="7"/>
       <c r="D129" s="1"/>
       <c r="F129" s="1"/>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="14"/>
       <c r="B130" s="1"/>
       <c r="C130" s="7"/>
       <c r="D130" s="1"/>
       <c r="F130" s="1"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="14"/>
       <c r="B131" s="1"/>
       <c r="C131" s="7"/>
       <c r="D131" s="1"/>
       <c r="F131" s="1"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="14"/>
       <c r="B132" s="1"/>
       <c r="C132" s="7"/>
       <c r="D132" s="1"/>
       <c r="F132" s="1"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="14"/>
       <c r="B133" s="1"/>
       <c r="C133" s="7"/>
@@ -10142,35 +10142,35 @@
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="14"/>
       <c r="B134" s="1"/>
       <c r="C134" s="7"/>
       <c r="D134" s="1"/>
       <c r="F134" s="1"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="14"/>
       <c r="B135" s="1"/>
       <c r="C135" s="7"/>
       <c r="D135" s="1"/>
       <c r="F135" s="1"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="14"/>
       <c r="B136" s="1"/>
       <c r="C136" s="7"/>
       <c r="D136" s="1"/>
       <c r="F136" s="1"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="14"/>
       <c r="B137" s="1"/>
       <c r="C137" s="7"/>
       <c r="D137" s="1"/>
       <c r="F137" s="1"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="7"/>
@@ -10178,7 +10178,7 @@
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="7"/>
@@ -10186,7 +10186,7 @@
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="7"/>
@@ -10194,7 +10194,7 @@
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="7"/>
@@ -10202,7 +10202,7 @@
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="7"/>
@@ -10210,7 +10210,7 @@
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="7"/>
@@ -10218,7 +10218,7 @@
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="7"/>
@@ -10226,7 +10226,7 @@
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="7"/>
@@ -10234,7 +10234,7 @@
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="7"/>
@@ -10242,7 +10242,7 @@
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="7"/>
@@ -10250,7 +10250,7 @@
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="7"/>
@@ -10258,63 +10258,63 @@
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="7"/>
@@ -10322,31 +10322,31 @@
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="7"/>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C163" s="7"/>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="7"/>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C165" s="7"/>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="7"/>
@@ -10354,23 +10354,23 @@
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="7"/>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C168" s="7"/>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="7"/>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C170" s="7"/>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="7"/>
@@ -10378,7 +10378,7 @@
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="7"/>
@@ -10386,7 +10386,7 @@
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="7"/>
@@ -10394,7 +10394,7 @@
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="7"/>
@@ -10402,7 +10402,7 @@
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="7"/>
@@ -10410,7 +10410,7 @@
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="7"/>
@@ -10418,7 +10418,7 @@
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="7"/>
@@ -10426,7 +10426,7 @@
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="7"/>
@@ -10434,7 +10434,7 @@
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="7"/>
@@ -10442,7 +10442,7 @@
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="7"/>
@@ -10450,7 +10450,7 @@
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="7"/>
@@ -10458,7 +10458,7 @@
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="7"/>
@@ -10466,7 +10466,7 @@
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="7"/>
@@ -10474,7 +10474,7 @@
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="7"/>
@@ -10482,7 +10482,7 @@
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="7"/>
@@ -10490,7 +10490,7 @@
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="7"/>
@@ -10498,7 +10498,7 @@
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="7"/>
@@ -10506,7 +10506,7 @@
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="7"/>
@@ -10514,7 +10514,7 @@
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="7"/>
@@ -10522,7 +10522,7 @@
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="7"/>
@@ -10530,7 +10530,7 @@
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="7"/>
@@ -10538,7 +10538,7 @@
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="7"/>
@@ -10546,7 +10546,7 @@
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="7"/>
@@ -10554,63 +10554,63 @@
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="D202" s="1"/>
@@ -10631,20 +10631,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36048042-5496-4822-BAA6-D0565889D478}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:O290"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" customWidth="1"/>
-    <col min="4" max="8" width="25.140625" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" customWidth="1"/>
-    <col min="10" max="11" width="25.140625" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" customWidth="1"/>
+    <col min="1" max="1" width="25.1796875" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" customWidth="1"/>
+    <col min="4" max="8" width="25.1796875" customWidth="1"/>
+    <col min="9" max="9" width="6.1796875" customWidth="1"/>
+    <col min="10" max="11" width="25.1796875" customWidth="1"/>
+    <col min="12" max="12" width="8.81640625" customWidth="1"/>
+    <col min="13" max="13" width="18.26953125" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>451</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>554</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>562</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>568</v>
       </c>
@@ -10814,7 +10814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>574</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>577</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>581</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>587</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>590</v>
       </c>
@@ -11028,7 +11028,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>593</v>
       </c>
@@ -11069,7 +11069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>597</v>
       </c>
@@ -11110,7 +11110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>600</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>602</v>
       </c>
@@ -11195,7 +11195,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>604</v>
       </c>
@@ -11236,7 +11236,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>606</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>608</v>
       </c>
@@ -11321,7 +11321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>610</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>613</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>615</v>
       </c>
@@ -11447,7 +11447,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>618</v>
       </c>
@@ -11491,7 +11491,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>621</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>623</v>
       </c>
@@ -11576,7 +11576,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>625</v>
       </c>
@@ -11617,7 +11617,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>627</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>630</v>
       </c>
@@ -11705,7 +11705,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>632</v>
       </c>
@@ -11746,7 +11746,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>635</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>637</v>
       </c>
@@ -11831,7 +11831,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>639</v>
       </c>
@@ -11875,7 +11875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>642</v>
       </c>
@@ -11919,7 +11919,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>644</v>
       </c>
@@ -11963,7 +11963,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>646</v>
       </c>
@@ -12004,7 +12004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>648</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>650</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>653</v>
       </c>
@@ -12133,7 +12133,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>655</v>
       </c>
@@ -12177,7 +12177,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>657</v>
       </c>
@@ -12221,7 +12221,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>659</v>
       </c>
@@ -12262,7 +12262,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>662</v>
       </c>
@@ -12306,7 +12306,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>664</v>
       </c>
@@ -12350,7 +12350,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>666</v>
       </c>
@@ -12394,7 +12394,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>668</v>
       </c>
@@ -12438,7 +12438,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>670</v>
       </c>
@@ -12479,7 +12479,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>672</v>
       </c>
@@ -12523,7 +12523,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>674</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>676</v>
       </c>
@@ -12605,7 +12605,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>678</v>
       </c>
@@ -12646,7 +12646,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>680</v>
       </c>
@@ -12690,7 +12690,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>682</v>
       </c>
@@ -12731,7 +12731,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>685</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>687</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>689</v>
       </c>
@@ -12863,7 +12863,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>691</v>
       </c>
@@ -12907,7 +12907,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>693</v>
       </c>
@@ -12948,7 +12948,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>695</v>
       </c>
@@ -12992,7 +12992,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>697</v>
       </c>
@@ -13036,7 +13036,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>699</v>
       </c>
@@ -13080,7 +13080,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>701</v>
       </c>
@@ -13121,7 +13121,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>703</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>705</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>707</v>
       </c>
@@ -13250,7 +13250,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>710</v>
       </c>
@@ -13291,7 +13291,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>712</v>
       </c>
@@ -13332,7 +13332,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>714</v>
       </c>
@@ -13373,7 +13373,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>716</v>
       </c>
@@ -13417,7 +13417,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>718</v>
       </c>
@@ -13461,7 +13461,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>720</v>
       </c>
@@ -13502,7 +13502,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>722</v>
       </c>
@@ -13543,7 +13543,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>724</v>
       </c>
@@ -13587,7 +13587,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>726</v>
       </c>
@@ -13628,7 +13628,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>728</v>
       </c>
@@ -13672,7 +13672,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>730</v>
       </c>
@@ -13716,7 +13716,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>732</v>
       </c>
@@ -13760,7 +13760,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>734</v>
       </c>
@@ -13804,7 +13804,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>736</v>
       </c>
@@ -13848,7 +13848,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>738</v>
       </c>
@@ -13892,7 +13892,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>740</v>
       </c>
@@ -13936,7 +13936,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>742</v>
       </c>
@@ -13977,7 +13977,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>744</v>
       </c>
@@ -14018,7 +14018,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>746</v>
       </c>
@@ -14059,7 +14059,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>748</v>
       </c>
@@ -14100,7 +14100,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>750</v>
       </c>
@@ -14141,7 +14141,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>752</v>
       </c>
@@ -14182,7 +14182,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>754</v>
       </c>
@@ -14223,7 +14223,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>756</v>
       </c>
@@ -14264,7 +14264,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>758</v>
       </c>
@@ -14305,7 +14305,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>760</v>
       </c>
@@ -14349,7 +14349,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>762</v>
       </c>
@@ -14390,7 +14390,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>764</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>766</v>
       </c>
@@ -14472,7 +14472,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>769</v>
       </c>
@@ -14516,7 +14516,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>771</v>
       </c>
@@ -14557,7 +14557,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>774</v>
       </c>
@@ -14598,7 +14598,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>776</v>
       </c>
@@ -14639,7 +14639,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>778</v>
       </c>
@@ -14680,7 +14680,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>780</v>
       </c>
@@ -14721,7 +14721,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>782</v>
       </c>
@@ -14762,7 +14762,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>784</v>
       </c>
@@ -14806,7 +14806,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>786</v>
       </c>
@@ -14850,7 +14850,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>788</v>
       </c>
@@ -14891,7 +14891,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>790</v>
       </c>
@@ -14932,7 +14932,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>792</v>
       </c>
@@ -14973,7 +14973,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>794</v>
       </c>
@@ -15014,7 +15014,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>796</v>
       </c>
@@ -15058,7 +15058,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>798</v>
       </c>
@@ -15102,7 +15102,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>800</v>
       </c>
@@ -15143,7 +15143,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>802</v>
       </c>
@@ -15184,7 +15184,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>804</v>
       </c>
@@ -15228,7 +15228,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>806</v>
       </c>
@@ -15269,7 +15269,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>808</v>
       </c>
@@ -15310,7 +15310,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>810</v>
       </c>
@@ -15354,7 +15354,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>812</v>
       </c>
@@ -15398,7 +15398,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>814</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>816</v>
       </c>
@@ -15483,7 +15483,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>818</v>
       </c>
@@ -15524,7 +15524,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>820</v>
       </c>
@@ -15565,7 +15565,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>822</v>
       </c>
@@ -15603,7 +15603,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>825</v>
       </c>
@@ -15644,7 +15644,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>827</v>
       </c>
@@ -15688,7 +15688,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>829</v>
       </c>
@@ -15729,7 +15729,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>831</v>
       </c>
@@ -15773,7 +15773,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>833</v>
       </c>
@@ -15814,7 +15814,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>835</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>837</v>
       </c>
@@ -15896,7 +15896,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>839</v>
       </c>
@@ -15937,7 +15937,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>841</v>
       </c>
@@ -15981,7 +15981,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>843</v>
       </c>
@@ -16025,7 +16025,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>845</v>
       </c>
@@ -16069,7 +16069,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>847</v>
       </c>
@@ -16110,7 +16110,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>849</v>
       </c>
@@ -16151,7 +16151,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>851</v>
       </c>
@@ -16192,7 +16192,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>853</v>
       </c>
@@ -16233,7 +16233,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>855</v>
       </c>
@@ -16274,7 +16274,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>857</v>
       </c>
@@ -16318,7 +16318,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>859</v>
       </c>
@@ -16359,7 +16359,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>861</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>863</v>
       </c>
@@ -16447,7 +16447,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>865</v>
       </c>
@@ -16488,7 +16488,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>867</v>
       </c>
@@ -16529,7 +16529,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>869</v>
       </c>
@@ -16570,7 +16570,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>871</v>
       </c>
@@ -16611,7 +16611,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>873</v>
       </c>
@@ -16652,7 +16652,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>875</v>
       </c>
@@ -16693,7 +16693,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>877</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>879</v>
       </c>
@@ -16775,7 +16775,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>881</v>
       </c>
@@ -16819,7 +16819,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>883</v>
       </c>
@@ -16863,7 +16863,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>885</v>
       </c>
@@ -16907,7 +16907,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>887</v>
       </c>
@@ -16951,7 +16951,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>889</v>
       </c>
@@ -16992,7 +16992,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>892</v>
       </c>
@@ -17033,7 +17033,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>894</v>
       </c>
@@ -17077,7 +17077,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>896</v>
       </c>
@@ -17118,7 +17118,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>898</v>
       </c>
@@ -17162,7 +17162,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>900</v>
       </c>
@@ -17200,7 +17200,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>902</v>
       </c>
@@ -17244,7 +17244,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>904</v>
       </c>
@@ -17288,7 +17288,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>906</v>
       </c>
@@ -17329,7 +17329,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>908</v>
       </c>
@@ -17370,7 +17370,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>910</v>
       </c>
@@ -17411,7 +17411,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>912</v>
       </c>
@@ -17452,7 +17452,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>914</v>
       </c>
@@ -17496,7 +17496,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>916</v>
       </c>
@@ -17540,7 +17540,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>918</v>
       </c>
@@ -17581,7 +17581,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>920</v>
       </c>
@@ -17622,7 +17622,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>922</v>
       </c>
@@ -17663,7 +17663,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>924</v>
       </c>
@@ -17704,7 +17704,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>926</v>
       </c>
@@ -17748,7 +17748,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>928</v>
       </c>
@@ -17789,7 +17789,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>930</v>
       </c>
@@ -17830,7 +17830,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>932</v>
       </c>
@@ -17871,7 +17871,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>934</v>
       </c>
@@ -17912,7 +17912,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>936</v>
       </c>
@@ -17953,7 +17953,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>938</v>
       </c>
@@ -17994,7 +17994,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>940</v>
       </c>
@@ -18035,7 +18035,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>942</v>
       </c>
@@ -18079,7 +18079,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>944</v>
       </c>
@@ -18120,7 +18120,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>946</v>
       </c>
@@ -18164,7 +18164,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>948</v>
       </c>
@@ -18205,7 +18205,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>950</v>
       </c>
@@ -18246,7 +18246,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>952</v>
       </c>
@@ -18287,7 +18287,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>954</v>
       </c>
@@ -18331,7 +18331,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>956</v>
       </c>
@@ -18372,7 +18372,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>958</v>
       </c>
@@ -18413,7 +18413,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>960</v>
       </c>
@@ -18454,7 +18454,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>962</v>
       </c>
@@ -18498,7 +18498,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>964</v>
       </c>
@@ -18539,7 +18539,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>966</v>
       </c>
@@ -18583,7 +18583,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>968</v>
       </c>
@@ -18624,7 +18624,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>970</v>
       </c>
@@ -18665,7 +18665,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>972</v>
       </c>
@@ -18706,7 +18706,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>974</v>
       </c>
@@ -18747,7 +18747,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>976</v>
       </c>
@@ -18788,7 +18788,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>978</v>
       </c>
@@ -18832,7 +18832,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>980</v>
       </c>
@@ -18876,7 +18876,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>982</v>
       </c>
@@ -18899,7 +18899,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>984</v>
       </c>
@@ -18919,7 +18919,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>988</v>
       </c>
@@ -18960,7 +18960,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>991</v>
       </c>
@@ -18998,7 +18998,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>995</v>
       </c>
@@ -19015,7 +19015,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>997</v>
       </c>
@@ -19059,7 +19059,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>1000</v>
       </c>
@@ -19079,7 +19079,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>1001</v>
       </c>
@@ -19102,7 +19102,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>1003</v>
       </c>
@@ -19122,7 +19122,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>1005</v>
       </c>
@@ -19145,7 +19145,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>1007</v>
       </c>
@@ -19168,7 +19168,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>1009</v>
       </c>
@@ -19206,7 +19206,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>1011</v>
       </c>
@@ -19229,7 +19229,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="209" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>1013</v>
       </c>
@@ -19255,7 +19255,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>1015</v>
       </c>
@@ -19296,7 +19296,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="211" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>1018</v>
       </c>
@@ -19319,7 +19319,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="212" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>1021</v>
       </c>
@@ -19360,7 +19360,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="213" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>1023</v>
       </c>
@@ -19401,7 +19401,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>1025</v>
       </c>
@@ -19427,7 +19427,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>1026</v>
       </c>
@@ -19441,7 +19441,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>1028</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>1029</v>
       </c>
@@ -19499,7 +19499,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>1031</v>
       </c>
@@ -19522,7 +19522,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="219" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>1032</v>
       </c>
@@ -19560,7 +19560,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>1034</v>
       </c>
@@ -19598,7 +19598,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="221" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>1037</v>
       </c>
@@ -19627,7 +19627,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="222" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>1039</v>
       </c>
@@ -19650,7 +19650,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="223" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>1040</v>
       </c>
@@ -19688,7 +19688,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="224" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>1042</v>
       </c>
@@ -19729,7 +19729,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>1045</v>
       </c>
@@ -19770,7 +19770,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>1047</v>
       </c>
@@ -19811,7 +19811,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>1049</v>
       </c>
@@ -19840,7 +19840,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>1052</v>
       </c>
@@ -19878,7 +19878,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>1054</v>
       </c>
@@ -19901,7 +19901,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>1055</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>1058</v>
       </c>
@@ -19983,7 +19983,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>1060</v>
       </c>
@@ -20024,7 +20024,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>1062</v>
       </c>
@@ -20062,7 +20062,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="234" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>1064</v>
       </c>
@@ -20082,7 +20082,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>1065</v>
       </c>
@@ -20120,7 +20120,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="236" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>1067</v>
       </c>
@@ -20143,7 +20143,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>1069</v>
       </c>
@@ -20184,7 +20184,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="238" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>1072</v>
       </c>
@@ -20207,7 +20207,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="239" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>1073</v>
       </c>
@@ -20227,7 +20227,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>1074</v>
       </c>
@@ -20265,7 +20265,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="241" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>1077</v>
       </c>
@@ -20285,7 +20285,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="242" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>1078</v>
       </c>
@@ -20308,7 +20308,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="243" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>1079</v>
       </c>
@@ -20346,7 +20346,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>1081</v>
       </c>
@@ -20369,7 +20369,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="245" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>1082</v>
       </c>
@@ -20392,7 +20392,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="246" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>1083</v>
       </c>
@@ -20415,7 +20415,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>1084</v>
       </c>
@@ -20429,7 +20429,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="248" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>1084</v>
       </c>
@@ -20449,7 +20449,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="249" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>1086</v>
       </c>
@@ -20469,7 +20469,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="250" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>1087</v>
       </c>
@@ -20510,7 +20510,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="251" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>1089</v>
       </c>
@@ -20530,7 +20530,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="252" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>1090</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="253" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>1092</v>
       </c>
@@ -20591,7 +20591,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>1093</v>
       </c>
@@ -20632,7 +20632,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="255" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>1095</v>
       </c>
@@ -20655,7 +20655,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="256" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>1096</v>
       </c>
@@ -20693,7 +20693,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="257" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>1098</v>
       </c>
@@ -20716,7 +20716,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>1099</v>
       </c>
@@ -20733,7 +20733,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>1101</v>
       </c>
@@ -20774,7 +20774,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>1104</v>
       </c>
@@ -20812,7 +20812,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>1106</v>
       </c>
@@ -20850,7 +20850,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="262" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>1108</v>
       </c>
@@ -20891,7 +20891,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>1110</v>
       </c>
@@ -20926,7 +20926,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="264" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>1111</v>
       </c>
@@ -20949,7 +20949,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>1112</v>
       </c>
@@ -20969,7 +20969,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>1113</v>
       </c>
@@ -21004,7 +21004,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="267" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>1115</v>
       </c>
@@ -21048,7 +21048,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>1117</v>
       </c>
@@ -21089,7 +21089,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>1119</v>
       </c>
@@ -21115,7 +21115,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>1121</v>
       </c>
@@ -21153,7 +21153,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="271" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>1123</v>
       </c>
@@ -21191,7 +21191,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>1125</v>
       </c>
@@ -21217,7 +21217,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>1127</v>
       </c>
@@ -21237,7 +21237,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>1128</v>
       </c>
@@ -21257,7 +21257,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="275" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>1129</v>
       </c>
@@ -21286,7 +21286,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>1131</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="277" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>1133</v>
       </c>
@@ -21344,7 +21344,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>1134</v>
       </c>
@@ -21373,7 +21373,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>1136</v>
       </c>
@@ -21411,7 +21411,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>1138</v>
       </c>
@@ -21452,7 +21452,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>1141</v>
       </c>
@@ -21490,7 +21490,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>1144</v>
       </c>
@@ -21513,7 +21513,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="283" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>1145</v>
       </c>
@@ -21554,7 +21554,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>1147</v>
       </c>
@@ -21577,7 +21577,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="285" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>1148</v>
       </c>
@@ -21600,7 +21600,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="286" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>1150</v>
       </c>
@@ -21644,7 +21644,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="287" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>1152</v>
       </c>
@@ -21667,7 +21667,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="288" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>1153</v>
       </c>
@@ -21705,7 +21705,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>1155</v>
       </c>
@@ -21734,7 +21734,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>1156</v>
       </c>
@@ -21792,13 +21792,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E76BC6-48F1-400D-81DC-1243D80FB9EE}">
   <dimension ref="A1:BG195"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="45.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="45"/>
+    <col min="1" max="1" width="45.26953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.7265625" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" s="42" customFormat="1" ht="209.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:59" s="42" customFormat="1" ht="204" x14ac:dyDescent="0.35">
       <c r="A1" s="43" t="s">
         <v>452</v>
       </c>
@@ -21866,7 +21866,7 @@
         <v>484</v>
       </c>
       <c r="W1" s="44" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="X1" s="42" t="s">
         <v>485</v>
@@ -21977,7 +21977,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="2" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>554</v>
       </c>
@@ -22135,7 +22135,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>562</v>
       </c>
@@ -22299,7 +22299,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>568</v>
       </c>
@@ -22436,7 +22436,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>574</v>
       </c>
@@ -22489,7 +22489,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>577</v>
       </c>
@@ -22635,7 +22635,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="7" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>581</v>
       </c>
@@ -22736,7 +22736,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="8" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>587</v>
       </c>
@@ -22876,7 +22876,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="9" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>590</v>
       </c>
@@ -23043,7 +23043,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="10" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>593</v>
       </c>
@@ -23174,7 +23174,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="11" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>597</v>
       </c>
@@ -23302,7 +23302,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="12" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>600</v>
       </c>
@@ -23451,7 +23451,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="13" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>602</v>
       </c>
@@ -23549,7 +23549,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="14" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>604</v>
       </c>
@@ -23647,7 +23647,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="15" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>606</v>
       </c>
@@ -23817,7 +23817,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="16" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>608</v>
       </c>
@@ -23927,7 +23927,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="17" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>610</v>
       </c>
@@ -24058,7 +24058,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="18" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>613</v>
       </c>
@@ -24189,7 +24189,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="19" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>615</v>
       </c>
@@ -24317,7 +24317,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>618</v>
       </c>
@@ -24484,7 +24484,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="21" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>621</v>
       </c>
@@ -24612,7 +24612,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="22" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>623</v>
       </c>
@@ -24776,7 +24776,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="23" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>625</v>
       </c>
@@ -24907,7 +24907,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="24" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>627</v>
       </c>
@@ -25059,7 +25059,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="25" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>630</v>
       </c>
@@ -25229,7 +25229,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>632</v>
       </c>
@@ -25312,7 +25312,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="27" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>635</v>
       </c>
@@ -25452,7 +25452,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="28" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>637</v>
       </c>
@@ -25622,7 +25622,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="29" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>639</v>
       </c>
@@ -25762,7 +25762,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="30" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>644</v>
       </c>
@@ -25887,7 +25887,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="31" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>646</v>
       </c>
@@ -26054,7 +26054,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="32" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>648</v>
       </c>
@@ -26221,7 +26221,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="33" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>650</v>
       </c>
@@ -26349,7 +26349,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="34" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>653</v>
       </c>
@@ -26480,7 +26480,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="35" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>655</v>
       </c>
@@ -26638,7 +26638,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="36" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>657</v>
       </c>
@@ -26805,7 +26805,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="37" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>659</v>
       </c>
@@ -26951,7 +26951,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="38" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>662</v>
       </c>
@@ -27124,7 +27124,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="39" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>664</v>
       </c>
@@ -27285,7 +27285,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="40" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>666</v>
       </c>
@@ -27440,7 +27440,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="41" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>668</v>
       </c>
@@ -27610,7 +27610,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="42" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>642</v>
       </c>
@@ -27780,7 +27780,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="43" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>670</v>
       </c>
@@ -27923,7 +27923,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="44" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>672</v>
       </c>
@@ -28036,7 +28036,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="45" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>674</v>
       </c>
@@ -28164,7 +28164,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="46" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>676</v>
       </c>
@@ -28295,7 +28295,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="47" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>678</v>
       </c>
@@ -28396,7 +28396,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="48" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>680</v>
       </c>
@@ -28566,7 +28566,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="49" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>682</v>
       </c>
@@ -28694,7 +28694,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="50" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>685</v>
       </c>
@@ -28825,7 +28825,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="51" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>687</v>
       </c>
@@ -28926,7 +28926,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="52" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>689</v>
       </c>
@@ -29099,7 +29099,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="53" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>691</v>
       </c>
@@ -29266,7 +29266,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="54" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>693</v>
       </c>
@@ -29430,7 +29430,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="55" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>695</v>
       </c>
@@ -29579,7 +29579,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="56" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>697</v>
       </c>
@@ -29662,7 +29662,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="57" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>699</v>
       </c>
@@ -29754,7 +29754,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="58" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>701</v>
       </c>
@@ -29876,7 +29876,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="59" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>703</v>
       </c>
@@ -30028,7 +30028,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="60" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>705</v>
       </c>
@@ -30201,7 +30201,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="61" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>707</v>
       </c>
@@ -30341,7 +30341,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="62" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>710</v>
       </c>
@@ -30466,7 +30466,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="63" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>712</v>
       </c>
@@ -30603,7 +30603,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="64" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>714</v>
       </c>
@@ -30629,7 +30629,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="65" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>716</v>
       </c>
@@ -30778,7 +30778,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="66" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>718</v>
       </c>
@@ -30927,7 +30927,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="67" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>720</v>
       </c>
@@ -31073,7 +31073,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="68" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>722</v>
       </c>
@@ -31207,7 +31207,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="69" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>724</v>
       </c>
@@ -31383,7 +31383,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="70" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>726</v>
       </c>
@@ -31535,7 +31535,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="71" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>728</v>
       </c>
@@ -31636,7 +31636,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="72" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>730</v>
       </c>
@@ -31806,7 +31806,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="73" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>732</v>
       </c>
@@ -31967,7 +31967,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="74" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>734</v>
       </c>
@@ -32110,7 +32110,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="75" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>736</v>
       </c>
@@ -32241,7 +32241,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="76" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>738</v>
       </c>
@@ -32384,7 +32384,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="77" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>740</v>
       </c>
@@ -32560,7 +32560,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="78" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>742</v>
       </c>
@@ -32694,7 +32694,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="79" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>744</v>
       </c>
@@ -32816,7 +32816,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="80" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>746</v>
       </c>
@@ -32977,7 +32977,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="81" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>748</v>
       </c>
@@ -33147,7 +33147,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="82" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>750</v>
       </c>
@@ -33299,7 +33299,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="83" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>752</v>
       </c>
@@ -33442,7 +33442,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="84" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>754</v>
       </c>
@@ -33573,7 +33573,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="85" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>756</v>
       </c>
@@ -33713,7 +33713,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="86" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>758</v>
       </c>
@@ -33850,7 +33850,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="87" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>760</v>
       </c>
@@ -33984,7 +33984,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="88" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>762</v>
       </c>
@@ -34118,7 +34118,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="89" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>764</v>
       </c>
@@ -34282,7 +34282,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="90" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>766</v>
       </c>
@@ -34437,7 +34437,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="91" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>769</v>
       </c>
@@ -34607,7 +34607,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="92" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>771</v>
       </c>
@@ -34705,7 +34705,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="93" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>774</v>
       </c>
@@ -34815,7 +34815,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="94" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>776</v>
       </c>
@@ -34979,7 +34979,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="95" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>778</v>
       </c>
@@ -35140,7 +35140,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="96" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>780</v>
       </c>
@@ -35265,7 +35265,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="97" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>782</v>
       </c>
@@ -35417,7 +35417,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="98" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>784</v>
       </c>
@@ -35560,7 +35560,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="99" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>786</v>
       </c>
@@ -35718,7 +35718,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="100" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>788</v>
       </c>
@@ -35837,7 +35837,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="101" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>790</v>
       </c>
@@ -35884,7 +35884,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="102" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>792</v>
       </c>
@@ -36012,7 +36012,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="103" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>794</v>
       </c>
@@ -36137,7 +36137,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="104" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>796</v>
       </c>
@@ -36313,7 +36313,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="105" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>798</v>
       </c>
@@ -36486,7 +36486,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="106" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>800</v>
       </c>
@@ -36644,7 +36644,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="107" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>802</v>
       </c>
@@ -36745,7 +36745,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="108" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>804</v>
       </c>
@@ -36915,7 +36915,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="109" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>806</v>
       </c>
@@ -37040,7 +37040,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="110" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>808</v>
       </c>
@@ -37102,7 +37102,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="111" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>810</v>
       </c>
@@ -37266,7 +37266,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="112" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>812</v>
       </c>
@@ -37394,7 +37394,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="113" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>814</v>
       </c>
@@ -37561,7 +37561,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="114" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>816</v>
       </c>
@@ -37638,7 +37638,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="115" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>818</v>
       </c>
@@ -37673,7 +37673,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="116" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>820</v>
       </c>
@@ -37837,7 +37837,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="117" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>822</v>
       </c>
@@ -37974,7 +37974,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="118" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>825</v>
       </c>
@@ -38126,7 +38126,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="119" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>827</v>
       </c>
@@ -38290,7 +38290,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="120" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>829</v>
       </c>
@@ -38463,7 +38463,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="121" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>831</v>
       </c>
@@ -38630,7 +38630,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="122" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>833</v>
       </c>
@@ -38689,7 +38689,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="123" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>835</v>
       </c>
@@ -38853,7 +38853,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="124" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>837</v>
       </c>
@@ -38984,7 +38984,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="125" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>839</v>
       </c>
@@ -39106,7 +39106,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="126" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>841</v>
       </c>
@@ -39270,7 +39270,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="127" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>843</v>
       </c>
@@ -39431,7 +39431,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="128" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>845</v>
       </c>
@@ -39607,7 +39607,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="129" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>847</v>
       </c>
@@ -39744,7 +39744,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="130" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>849</v>
       </c>
@@ -39878,7 +39878,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="131" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>851</v>
       </c>
@@ -39997,7 +39997,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="132" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>853</v>
       </c>
@@ -40167,7 +40167,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="133" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>855</v>
       </c>
@@ -40217,7 +40217,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="134" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>857</v>
       </c>
@@ -40357,7 +40357,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="135" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>859</v>
       </c>
@@ -40485,7 +40485,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="136" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>861</v>
       </c>
@@ -40649,7 +40649,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="137" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>863</v>
       </c>
@@ -40822,7 +40822,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="138" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>865</v>
       </c>
@@ -40992,7 +40992,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="139" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>867</v>
       </c>
@@ -41129,7 +41129,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="140" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>869</v>
       </c>
@@ -41266,7 +41266,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="141" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>871</v>
       </c>
@@ -41382,7 +41382,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="142" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>873</v>
       </c>
@@ -41516,7 +41516,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="143" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>875</v>
       </c>
@@ -41668,7 +41668,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="144" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>877</v>
       </c>
@@ -41808,7 +41808,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="145" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>879</v>
       </c>
@@ -41963,7 +41963,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="146" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>881</v>
       </c>
@@ -42109,7 +42109,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="147" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>883</v>
       </c>
@@ -42195,7 +42195,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="148" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>885</v>
       </c>
@@ -42293,7 +42293,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="149" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>887</v>
       </c>
@@ -42400,7 +42400,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="150" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>889</v>
       </c>
@@ -42504,7 +42504,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="151" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>892</v>
       </c>
@@ -42548,7 +42548,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="152" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>894</v>
       </c>
@@ -42688,7 +42688,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="153" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>896</v>
       </c>
@@ -42807,7 +42807,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="154" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>898</v>
       </c>
@@ -42986,7 +42986,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="155" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>900</v>
       </c>
@@ -43129,7 +43129,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="156" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>902</v>
       </c>
@@ -43239,7 +43239,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="157" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>904</v>
       </c>
@@ -43412,7 +43412,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="158" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>906</v>
       </c>
@@ -43495,7 +43495,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="159" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>908</v>
       </c>
@@ -43626,7 +43626,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="160" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>910</v>
       </c>
@@ -43760,7 +43760,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="161" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>912</v>
       </c>
@@ -43864,7 +43864,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="162" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>914</v>
       </c>
@@ -44010,7 +44010,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="163" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>916</v>
       </c>
@@ -44174,7 +44174,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="164" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>918</v>
       </c>
@@ -44284,7 +44284,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="165" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>920</v>
       </c>
@@ -44421,7 +44421,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="166" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>922</v>
       </c>
@@ -44588,7 +44588,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="167" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>924</v>
       </c>
@@ -44725,7 +44725,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="168" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>926</v>
       </c>
@@ -44859,7 +44859,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="169" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>928</v>
       </c>
@@ -44993,7 +44993,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="170" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>930</v>
       </c>
@@ -45139,7 +45139,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="171" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>932</v>
       </c>
@@ -45255,7 +45255,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="172" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>936</v>
       </c>
@@ -45410,7 +45410,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="173" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>938</v>
       </c>
@@ -45574,7 +45574,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="174" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>940</v>
       </c>
@@ -45702,7 +45702,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="175" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>942</v>
       </c>
@@ -45872,7 +45872,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="176" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>944</v>
       </c>
@@ -45973,7 +45973,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="177" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>946</v>
       </c>
@@ -46101,7 +46101,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="178" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>948</v>
       </c>
@@ -46268,7 +46268,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="179" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>1160</v>
       </c>
@@ -46426,7 +46426,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="180" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>950</v>
       </c>
@@ -46536,7 +46536,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="181" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>952</v>
       </c>
@@ -46604,7 +46604,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="182" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>954</v>
       </c>
@@ -46780,7 +46780,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="183" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>956</v>
       </c>
@@ -46938,7 +46938,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="184" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>958</v>
       </c>
@@ -47051,7 +47051,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="185" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>960</v>
       </c>
@@ -47185,7 +47185,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="186" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>962</v>
       </c>
@@ -47364,7 +47364,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="187" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>964</v>
       </c>
@@ -47519,7 +47519,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="188" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>966</v>
       </c>
@@ -47665,7 +47665,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="189" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>968</v>
       </c>
@@ -47814,7 +47814,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="190" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>970</v>
       </c>
@@ -47933,7 +47933,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="191" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>972</v>
       </c>
@@ -48064,7 +48064,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="192" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>974</v>
       </c>
@@ -48234,7 +48234,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="193" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>976</v>
       </c>
@@ -48389,7 +48389,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="194" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>978</v>
       </c>
@@ -48535,7 +48535,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="195" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>980</v>
       </c>
@@ -48723,6 +48723,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010018141AFBEDAA4E4F8F497BA0BA465628" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="51632a301ac108a956373b15242a2c1c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3740b2bf-318f-4c2d-92fe-b8cc5ab95724" xmlns:ns4="0d38da4c-d0a5-4e53-81d3-71f1e08ba0ee" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8aed9f36c2f7cc18b5698afd23e33de4" ns3:_="" ns4:_="">
     <xsd:import namespace="3740b2bf-318f-4c2d-92fe-b8cc5ab95724"/>
@@ -48951,22 +48966,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2FF79C2-D6CA-4146-8A33-8B2F68A6926A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8B78A5C-B87B-48A6-A425-F525FA87B0A7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{629B1C7C-1368-414C-B746-5D693F4D5577}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -48983,21 +49000,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8B78A5C-B87B-48A6-A425-F525FA87B0A7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2FF79C2-D6CA-4146-8A33-8B2F68A6926A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>